--- a/frontend/public/wbs-upload-template.xlsx
+++ b/frontend/public/wbs-upload-template.xlsx
@@ -34,7 +34,7 @@
     <t>Review the structure model and highlight clashes</t>
   </si>
   <si>
-    <t>ID Coordination</t>
+    <t>ID - RCP Coordination</t>
   </si>
   <si>
     <t>Electrical distribution strategy</t>
